--- a/src/main/resources/espacios/software/Java OPP.xlsx
+++ b/src/main/resources/espacios/software/Java OPP.xlsx
@@ -5,10 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="1 OOP" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="2 OOP" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="3 OOP" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="4 OOP" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="5 OOP" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="6 OOP" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="535">
   <si>
     <t xml:space="preserve">What is OOP?</t>
   </si>
@@ -227,6 +232,1404 @@
   </si>
   <si>
     <t xml:space="preserve">which will set the value of x to 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By now, you are quite familiar with the public keyword that appears in almost all of our examples:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The public keyword is an access modifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meaning that it is used to set the access level for classes, attributes, methods and constructors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We divide modifiers into two groups:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access Modifiers - controls the access level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Access Modifiers - do not control access level, but provides other functionality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access Modifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For classes, you can use either public or default:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">public: The class is accessible by any other class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default: The class is only accessible by classes in the same package.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is used when you don't specify a modifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For attributes, methods and constructors, you can use the one of the following:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">public:	The code is accessible for all classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">private: The code is only accessible within the declared class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default: The code is only accessible in the same package. This is used when you don't specify a modifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protected: The code is accessible in the same package and subclasses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Access Modifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For classes, you can use either final or abstract:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final: The class cannot be inherited by other classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abstract: The class cannot be used to create objects (To access an abstract class, it must be inherited from another class)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For attributes and methods, you can use the one of the following:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final: Attributes and methods cannot be overridden/modified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">static: Attributes and methods belongs to the class, rather than an object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abstract: Can only be used in an abstract class, and can only be used on methods.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The method does not have a body, for example abstract void run();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The body is provided by the subclass (inherited from).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transient: Attributes and methods are skipped when serializing the object containing them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">synchronized: Methods can only be accessed by one thread at a time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volatile: The value of an attribute is not cached thread-locally, and is always read from the "main memory"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you don't want the ability to override existing attribute values, declare attributes as final:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Static</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A static method means that it can be accessed without creating an object of the class, unlike public:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abstract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An abstract method belongs to an abstract class, and it does not have a body.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The body is provided by the subclass:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encapsulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The meaning of Encapsulation, is to make sure that "sensitive" data is hidden from users.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To achieve this, you must:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">declare class variables/attributes as private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">provide public get and set methods to access and update the value of a private variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get and Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You learned from the previous chapter that private variables can only be accessed within the same class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(an outside class has no access to it).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">However, it is possible to access them if we provide public get and set methods.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The get method returns the variable value, and the set method sets the value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syntax for both is that they start with either get or set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">followed by the name of the variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">with the first letter in upper case:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example explained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The get method returns the value of the variable name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The set method takes a parameter (newName) and assigns it to the name variable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The this keyword is used to refer to the current object.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">However, as the name variable is declared as private, we cannot access it from outside this class:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the variable was declared as public, we would expect the following output: John</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instead, we use the getName() and setName() methods to access and update the variable:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Java Packages &amp; API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A package in Java is used to group related classes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Think of it as a folder in a file directory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We use packages to avoid name conflicts, and to write a better maintainable code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packages are divided into two categories:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built-in Packages (packages from the Java API)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User-defined Packages (create your own packages)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built-in Packages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Java API is a library of prewritten classes, that are free to use, included in the Java Development Environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The library contains components for managing input, database programming, and much much more.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The library is divided into packages and classes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meaning you can either import a single class (along with its methods and attributes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">or a whole package that contain all the classes that belong to the specified package.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To use a class or a package from the library, you need to use the import keyword:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import a Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you find a class you want to use, for example, the Scanner class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which is used to get user input, write the following code:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the example above, java.util is a package, while Scanner is a class of the java.util package.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inheritance (Subclass and Superclass)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Java, it is possible to inherit attributes and methods from one class to another.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We group the "inheritance concept" into two categories:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subclass (child): the class that inherits from another class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">superclass (parent): the class being inherited from</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To inherit from a class, use the extends keyword.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the example below, the Car class (subclass) inherits the attributes and methods from the Vehicle class (superclass):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you notice the protected modifier in Vehicle?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We set the brand attribute in Vehicle to a protected access modifier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If it was set to private, the Car class would not be able to access it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why And When To Use "Inheritance"?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- It is useful for code reusability: reuse attributes and methods of an existing class when you create a new class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polymorphism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polymorphism means "many forms", and it occurs when we have many classes that are related to each other by inheritance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Like we specified in the previous chapter;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inheritance lets us inherit attributes and methods from another class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polymorphism uses those methods to perform different tasks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This allows us to perform a single action in different ways.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For example, think of a superclass called Animal that has a method called animalSound().</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subclasses of Animals could be Pigs, Cats, Dogs, Birds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">And they also have their own implementation of an animal sound (the pig oinks, and the cat meows, etc.):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remember from the Inheritance chapter that we use the extends keyword to inherit from a class. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why And When To Use "Inheritance" and "Polymorphism"?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inner Classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Java, it is also possible to nest classes (a class within a class).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The purpose of nested classes is to group classes that belong together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which makes your code more readable and maintainable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To access the inner class, create an object of the outer class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and then create an object of the inner class:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private Inner Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlike a "regular" class, an inner class can be private or protected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you don't want outside objects to access the inner class, declare the class as private:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you try to access a private inner class from an outside class, an error occurs:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abstract Classes and Methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data abstraction is the process of hiding certain details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and showing only essential information to the user.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abstraction can be achieved with either abstract classes or interfaces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(which you will learn more about in the next chapter).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The abstract keyword is a non-access modifier, used for classes and methods:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abstract class: is a restricted class that cannot be used to create objects (to access it, it must be inherited from another class).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abstract method: can only be used in an abstract class, and it does not have a body.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An abstract class can have both abstract and regular methods:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From the example above, it is not possible to create an object of the Animal class: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">To access the abstract class, it must be inherited from another class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let's convert the Animal class we used in the Polymorphism chapter to an abstract class:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remember from the Inheritance chapter that we use the extends keyword to inherit from a class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why And When To Use Abstract Classes and Methods?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To achieve security - hide certain details and only show the important details of an object.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: Abstraction can also be achieved with Interfaces,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which you will learn more about in the next chapter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interfaces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Another way to achieve abstraction in Java, is with interfaces.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An interface is a completely "abstract class" that is used to group related methods with empty bodies:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To access the interface methods, the interface must be "implemented" (kinda like inherited)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">by another class with the implements keyword (instead of extends).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The body of the interface method is provided by the "implement" class:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes on Interfaces:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Like abstract classes, interfaces cannot be used to create objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(in the example above, it is not possible to create an "Animal" object in the MyMainClass)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interface methods do not have a body - the body is provided by the "implement" class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On implementation of an interface, you must override all of its methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interface methods are by default abstract and public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interface attributes are by default public, static and final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An interface cannot contain a constructor (as it cannot be used to create objects)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why And When To Use Interfaces?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) To achieve security - hide certain details and only show the important details of an object (interface).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2) Java does not support "multiple inheritance"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(a class can only inherit from one superclass).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">However, it can be achieved with interfaces, because the class can implement multiple interfaces.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: To implement multiple interfaces, separate them with a comma (see example below).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enums</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An enum is a special "class" that represents a group of constants (unchangeable variables, like final variables).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To create an enum, use the enum keyword (instead of class or interface)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and separate the constants with a comma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note that they should be in uppercase letters:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can access enum constants with the dot syntax: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enum inside a Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can also have an enum inside a class:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enum in a Switch Statement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enums are often used in switch statements to check for corresponding values:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop Through an Enum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The enum type has a values() method, which returns an array of all enum constants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This method is useful when you want to loop through the constants of an enum:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference between Enums and Classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An enum can, just like a class, have attributes and methods.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only difference is that enum constants are public, static and final (unchangeable - cannot be overridden).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An enum cannot be used to create objects, and it cannot extend other classes (but it can implement interfaces).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why And When To Use Enums?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use enums when you have values that you know aren't going to change, like month days, days, colors, deck of cards, etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date and Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Java Dates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Java does not have a built-in Date class, but we can import the java.time package to work with the date and time API.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The package includes many date and time classes. For example:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LocalDate: Represents a date (year, month, day (yyyy-MM-dd))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LocalTime: Represents a time (hour, minute, second and nanoseconds (HH-mm-ss-ns))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LocalDateTime: Represents both a date and a time (yyyy-MM-dd-HH-mm-ss-ns)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DateTimeFormatter: Formatter for displaying and parsing date-time objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Display Current Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To display the current date, import the java.time.LocalDate class, and use its now() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Display Current Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To display the current time (hour, minute, second, and nanoseconds), import the java.time.LocalTime class, and use its now() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Display Current Date and Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To display the current date and time, import the java.time.LocalDateTime class, and use its now() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formatting Date and Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The "T" in the example above is used to separate the date from the time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can use the DateTimeFormatter class with the ofPattern() method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in the same package to format or parse date-time objects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The following example will remove both the "T" and nanoseconds from the date-time:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ofPattern() method accepts all sorts of values, if you want to display the date and time in a different format. For example:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArrayList</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ArrayList class is a resizable array, which can be found in the java.util package.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The difference between a built-in array and an ArrayList in Java</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is that the size of an array cannot be modified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(if you want to add or remove elements to/from an array, you have to create a new one).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While elements can be added and removed from an ArrayList whenever you want.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The syntax is also slightly different:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ArrayList class has many useful methods.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For example, to add elements to the list, use the add() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can also add an item at a specified position by referring to the index number:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remember: Array indexes start with 0: [0] is the first element. [1] is the second element, etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access an Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To access an element in the ArrayList, use the get() method and refer to the index number:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change an Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To modify an element, use the set() method and refer to the index number:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove an Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To remove an element, use the remove() method and refer to the index number:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To remove all the elements in the ArrayList, use the clear() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArrayList Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To find out how many elements an ArrayList have, use the size method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop Through an ArrayList</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop through the elements of an ArrayList with a for loop, and use the size() method to specify how many times the loop should run:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elements in an ArrayList are actually objects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the examples above, we created elements (objects) of type "String".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remember that a String in Java is an object (not a primitive type).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To use other types, such as int, you must specify an equivalent wrapper class: Integer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For other primitive types, use: Boolean for boolean, Character for char, Double for double, etc:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort an ArrayList</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Another useful class in the java.util package is the Collections class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which include the sort() method for sorting lists alphabetically or numerically:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort an ArrayList of Integers: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedList</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the previous chapter, you learned about the ArrayList class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The LinkedList class is almost identical to the ArrayList:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArrayList vs. LinkedList</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The LinkedList class is a collection which can contain many objects of the same type, just like the ArrayList.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The LinkedList class has all of the same methods as the ArrayList class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">because they both implement the List interface.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This means that you can add items, change items, remove items and clear the list in the same way.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">However, while the ArrayList class and the LinkedList class can be used in the same way, they are built very differently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How the ArrayList works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ArrayList class has a regular array inside it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When an element is added, it is placed into the array.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the array is not big enough, a new, larger array is created to replace the old one and the old one is removed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How the LinkedList works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The LinkedList stores its items in "containers." The list has a link to the first container</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and each container has a link to the next container in the list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To add an element to the list, the element is placed into a new container</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and that container is linked to one of the other containers in the list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When To Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use an ArrayList for storing and accessing data, and LinkedList to manipulate data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LinkedList Methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For many cases, the ArrayList is more efficient as it is common to need access to random items in the list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">but the LinkedList provides several methods to do certain operations more efficiently:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Java Sort a List</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the previous chapters, you learned how to use two popular lists in Java:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArrayList and LinkedList, which are found in the java.util package.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which include the sort() method for sorting lists alphabetically or numerically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort an ArrayList of Strings alphabetically in ascending order:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort an ArrayList of Integers numerically in ascending order:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse the Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can also sort a list in reverse order, by using the reverseOrder() method.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the following example, we sort an ArrayList of Strings alphabetically in reverse/descending order:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort an ArrayList of Integers numerically in reverse/descending order:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashMap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the ArrayList chapter, you learned that Arrays store items as an ordered collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and you have to access them with an index number (int type).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A HashMap however, store items in "key/value" pairs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and you can access them by an index of another type (e.g. a String).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One object is used as a key (index) to another object (value).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It can store different types: String keys and Integer values,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">or the same type, like: String keys and String values:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The HashMap class has many useful methods. For example, to add items to it, use the put() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To access a value in the HashMap, use the get() method and refer to its key:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To remove an item, use the remove() method and refer to the key:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To remove all items, use the clear() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashMap Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To find out how many items there are, use the size() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop Through a HashMap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop through the items of a HashMap with a for-each loop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: Use the keySet() method if you only want the keys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and use the values() method if you only want the values:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A HashSet is a collection of items where every item is unique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and it is found in the java.util package:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The HashSet class has many useful methods. For example, to add items to it, use the add() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: In the example above, even though BMW is added twice it only appears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">once in the set because every item in a set has to be unique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check If an Item Exists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To check whether an item exists in a HashSet, use the contains() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To remove an item, use the remove() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Java Iterator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Iterator is an object that can be used to loop through collections, like ArrayList and HashSet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is called an "iterator" because "iterating" is the technical term for looping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To use an Iterator, you must import it from the java.util package.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Getting an Iterator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The iterator() method can be used to get an Iterator for any collection:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Looping Through a Collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To loop through a collection, use the hasNext() and next() methods of the Iterator:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrapper Classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrapper classes provide a way to use primitive data types (int, boolean, etc..) as objects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The table below shows the primitive type and the equivalent wrapper class:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sometimes you must use wrapper classes, for example when working with Collection objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">such as ArrayList, where primitive types cannot be used (the list can only store objects):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creating Wrapper Objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To create a wrapper object, use the wrapper class instead of the primitive type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To get the value, you can just print the object:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since you're now working with objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">you can use certain methods to get information about the specific object.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For example, the following methods are used to get the value associated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">with the corresponding wrapper object:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intValue(), byteValue(), shortValue(), longValue(), floatValue(), doubleValue(), charValue(), booleanValue().</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This example will output the same result as the example above:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Another useful method is the toString() method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which is used to convert wrapper objects to strings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the following example, we convert an Integer to a String</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and use the length() method of the String class to output the length of the "string":</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exceptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When executing Java code, different errors can occur:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coding errors made by the programmer, errors due to wrong input, or other unforeseeable things.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When an error occurs, Java will normally stop and generate an error message.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The technical term for this is: Java will throw an exception (throw an error).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">try and catch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The try statement allows you to define a block of code to be tested for errors while it is being executed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The catch statement allows you to define a block of code to be executed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if an error occurs in the try block.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The try and catch keywords come in pairs:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consider the following example:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This will generate an error, because myNumbers[10] does not exist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The output will be something like this:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: ArrayIndexOutOfBoundsException occurs when you try to access an index number that does not exist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If an error occurs, we can use try...catch to catch the error and execute some code to handle it:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The finally statement lets you execute code, after try...catch, regardless of the result:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is a Regular Expression?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A regular expression is a sequence of characters that forms a search pattern.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you search for data in a text, you can use this search pattern to describe what you are searching for.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A regular expression can be a single character, or a more complicated pattern.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular expressions can be used to perform all types of text search and text replace operations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Java does not have a built-in Regular Expression class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">but we can import the java.util.regex package to work with regular expressions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The package includes the following classes:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pattern Class - Defines a pattern (to be used in a search)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matcher Class - Used to search for the pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PatternSyntaxException Class - Indicates syntax error in a regular expression pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example Explained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In this example, The word "w3schools" is being searched for in a sentence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First, the pattern is created using the Pattern.compile() method.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The first parameter indicates which pattern is being searched for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and the second parameter has a flag to indicates that the search should be case-insensitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The second parameter is optional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The matcher() method is used to search for the pattern in a string.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It returns a Matcher object which contains information about the search that was performed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The find() method returns true if the pattern was found in the string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and false if it was not found.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flags in the compile() method change how the search is performed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here are a few of them:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pattern.CASE_INSENSITIVE - The case of letters will be ignored when performing a search.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pattern.LITERAL - Special characters in the pattern will not have any special meaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and will be treated as ordinary characters when performing a search.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pattern.UNICODE_CASE - Use it together with the CASE_INSENSITIVE flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to also ignore the case of letters outside of the English alphabet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regular Expression Patterns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The first parameter of the Pattern.compile() method is the pattern.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It describes what is being searched for.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brackets are used to find a range of characters:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[abc] - Find one character from the options between the brackets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[^abc] - Find one character NOT between the brackets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0-9] - Find one character from the range 0 to 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metacharacters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metacharacters are characters with a special meaning:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|	Find a match for any one of the patterns separated by | as in: cat|dog|fish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.	Find just one instance of any character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">^	Finds a match as the beginning of a string as in: ^Hello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$	Finds a match at the end of the string as in: World$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\d	Find a digit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\s	Find a whitespace character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\b	Find a match at the beginning of a word like this: \bWORD, or at the end of a word like this: WORD\b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">\uxxxx	Find the Unicode character specified by the hexadecimal number xxxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantifiers define quantities:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n+	Matches any string that contains at least one n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n*	Matches any string that contains zero or more occurrences of n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n?	Matches any string that contains zero or one occurrences of n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n{x}	Matches any string that contains a sequence of X n's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n{x,y}	Matches any string that contains a sequence of X to Y n's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n{x,}	Matches any string that contains a sequence of at least X n's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threads allows a program to operate more efficiently by doing multiple things at the same time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threads can be used to perform complicated tasks in the background without interrupting the main program.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creating a Thread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There are two ways to create a thread.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It can be created by extending the Thread class and overriding its run() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Another way to create a thread is to implement the Runnable interface:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running Threads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the class extends the Thread class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the thread can be run by creating an instance of the class and call its start() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the class implements the Runnable interface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the thread can be run by passing an instance of the class to a Thread object's constructor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and then calling the thread's start() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Differences between "extending" and "implementing" Threads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The major difference is that when a class extends the Thread class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">you cannot extend any other class, but by implementing the Runnable interface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it is possible to extend from another class as well, like: class MyClass extends OtherClass implements Runnable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concurrency Problems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Because threads run at the same time as other parts of the program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">there is no way to know in which order the code will run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When the threads and main program are reading and writing the same variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the values are unpredictable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The problems that result from this are called concurrency problems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To avoid concurrency problems, it is best to share as few attributes between threads as possible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If attributes need to be shared, one possible solution is to use the isAlive() method of the thread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to check whether the thread has finished running before using any attributes that the thread can change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lambda Expressions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lambda Expressions were added in Java 8.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A lambda expression is a short block of code which takes in parameters and returns a value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lambda expressions are similar to methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">but they do not need a name and they can be implemented right in the body of a method.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syntax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The simplest lambda expression contains a single parameter and an expression:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To use more than one parameter, wrap them in parentheses:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expressions are limited.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They have to immediately return a value, and they cannot contain variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assignments or statements such as if or for.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In order to do more complex operations, a code block can be used with curly braces.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the lambda expression needs to return a value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">then the code block should have a return statement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using Lambda Expressions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lambda expressions are usually passed as parameters to a function:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lambda expressions can be stored in variables if the variable's type is an interface which has only one method.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The lambda expression should have the same number of parameters and the same return type as that method.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Java has many of these kinds of interfaces built in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">such as the Consumer interface (found in the java.util package) used by lists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use Java's Consumer interface to store a lambda expression in a variable: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">To use a lambda expression in a method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the method should have a parameter with a single-method interface as its type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calling the interface's method will run the lambda expression:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a method which takes a lambda expression as a parameter: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Sorting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the List Sorting Chapter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">you learned how to sort lists alphabetically and numerically</t>
+  </si>
+  <si>
+    <t xml:space="preserve">but what if the list has objects in it?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To sort objects you need to specify a rule that decides how objects should be sorted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For example, if you have a list of cars you might want to sort them by year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the rule could be that cars with an earlier year go first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Comparator and Comparable interfaces allow you to specify what rule is used to sort objects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Being able to specify a sorting rule also allows you to change how strings and numbers are sorted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An object that implements the Comparator interface is called a comparator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Comparator interface allows you to create a class with a compare() method that compares two objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to decide which one should go first in a list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The compare() method should return a number which is:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative if the first object should go first in a list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive if the second object should go first in a list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero if the order does not matter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A class that implements the Comparator interface might look something like this:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To use the comparator, pass it as an argument into a sorting method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here is a complete example using a comparator to sort a list of cars by year:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using a Lambda Expression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To make the code shorter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the comparator can be replaced with a lambda expression which has the same arguments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and return value as the compare() method:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use a lambda expression as a comparator: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Comparable Interface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Comparable interface allows an object to specify its own sorting rule with a compareTo() method.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The compareTo() method takes an object as an argument</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and compares the comparable with the argument to decide which one should go first in a list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Like the comparator, the compareTo() method returns a number which is:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative if the comparable should go first in a list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive if the other object should go first in a list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Many native Java classes implement the Comparable interface, such as String and Integer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is why strings and numbers do not need a comparator to be sorted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An object that implements the Comparable interface might look something like this:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparator vs. Comparable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A comparator is an object with one method that is used to compare two different objects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A comparable is an object which can compare itself with other objects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is easier to use the Comparable interface when possible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">but the Comparator interface is more powerful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">because it allows you to sort any kind of object even if you cannot change its code.</t>
   </si>
 </sst>
 </file>
@@ -236,7 +1639,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -262,6 +1665,17 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -313,7 +1727,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -327,6 +1741,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -750,6 +2176,3527 @@
         <a:xfrm>
           <a:off x="9971280" y="37668240"/>
           <a:ext cx="4152960" cy="2838240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1561680</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>780480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Image 12" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9971280" y="41953680"/>
+          <a:ext cx="1561680" cy="780480"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>811080</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>2095200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Image 13" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9971280" y="49975200"/>
+          <a:ext cx="5486760" cy="2095200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>2160</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>3476160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Image 14" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9971280" y="52868160"/>
+          <a:ext cx="4677840" cy="3476160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4572360</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>3920040</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Image 15" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9971280" y="57546360"/>
+          <a:ext cx="4572360" cy="3920040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3647880</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>2790720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Image 16" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9971280" y="63556560"/>
+          <a:ext cx="3647880" cy="2790720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2952720</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>1523520</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Image 17" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId17"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9971280" y="68298120"/>
+          <a:ext cx="2952720" cy="1523520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>20160</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>1780920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Image 18" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9971280" y="70292520"/>
+          <a:ext cx="4695840" cy="1780920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3790800</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1447560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Image 19" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="1300320"/>
+          <a:ext cx="3790800" cy="1447560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1952280</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>580680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Image 20" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="4600080"/>
+          <a:ext cx="1952280" cy="580680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4646520</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>2409840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Image 21" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="6951960"/>
+          <a:ext cx="4646520" cy="2409840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3676680</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>3076560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Image 22" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="12321720"/>
+          <a:ext cx="3676680" cy="3076560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4095720</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>4886640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Image 23" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="17006400"/>
+          <a:ext cx="4095720" cy="4886640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4067280</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>3143160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Image 24" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="22874040"/>
+          <a:ext cx="4067280" cy="3143160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4362480</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>2743200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Image 25" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="27412200"/>
+          <a:ext cx="4362480" cy="2743200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>200520</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>685440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Image 26" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="30774600"/>
+          <a:ext cx="4972320" cy="685440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2609640</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>1399680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Image 27" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="32340600"/>
+          <a:ext cx="2609640" cy="1399680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3933720</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>847440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Image 28" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="35545320"/>
+          <a:ext cx="3933720" cy="847440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3209760</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>4334040</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Image 29" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="37044000"/>
+          <a:ext cx="3209760" cy="4334040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4667400</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>1171080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Image 30" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="43056000"/>
+          <a:ext cx="4667400" cy="1171080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4524480</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>4390920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Image 31" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11834640" y="45436680"/>
+          <a:ext cx="4524480" cy="4390920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1514160</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1161720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Image 32" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="0"/>
+          <a:ext cx="1514160" cy="1161720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2523960</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>590040</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Image 33" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="2055600"/>
+          <a:ext cx="2523960" cy="590040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3000240</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>2971800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Image 34" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="3494880"/>
+          <a:ext cx="3000240" cy="2971800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3095640</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>4695840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Image 35" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="7288560"/>
+          <a:ext cx="3095640" cy="4695840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2571480</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1876320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Image 36" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="12819240"/>
+          <a:ext cx="2571480" cy="1876320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4048200</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>2352600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Image 37" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="18999720"/>
+          <a:ext cx="4048200" cy="2352600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4734000</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>2247840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Image 38" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="22696200"/>
+          <a:ext cx="4734000" cy="2247840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4200480</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>2285640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Image 39" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="25599960"/>
+          <a:ext cx="4200480" cy="2285640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5457960</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>3276360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Image 40" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="28892520"/>
+          <a:ext cx="5457960" cy="3276360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3390840</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>1695240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Image 41" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="33310800"/>
+          <a:ext cx="3390840" cy="1695240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5210280</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>1209240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Image 42" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="35546760"/>
+          <a:ext cx="5210280" cy="1209240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3476520</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>2314440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="Image 43" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="38221200"/>
+          <a:ext cx="3476520" cy="2314440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4810320</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>2600280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Image 44" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="41188680"/>
+          <a:ext cx="4810320" cy="2600280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3909960</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>2669400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Image 45" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="44424720"/>
+          <a:ext cx="3909960" cy="2669400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3954600</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>2019600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Image 46" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="47786760"/>
+          <a:ext cx="3954600" cy="2019600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3959280</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>2449440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Image 47" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="50291280"/>
+          <a:ext cx="3959280" cy="2449440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3918240</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>2630520</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Image 48" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId17"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="53238240"/>
+          <a:ext cx="3918240" cy="2630520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4008960</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>2221920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Image 49" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="56500920"/>
+          <a:ext cx="4008960" cy="2221920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4730400</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>2971440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Image 50" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId19"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="59195160"/>
+          <a:ext cx="4730400" cy="2971440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4286160</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>2923920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Image 51" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId20"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="63298080"/>
+          <a:ext cx="4286160" cy="2923920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4029120</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>3200400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Image 52" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId21"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="67547520"/>
+          <a:ext cx="4029120" cy="3200400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3943440</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>3591000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Image 53" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId22"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="71367480"/>
+          <a:ext cx="3943440" cy="3591000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3809880</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>2867040</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Image 54" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId23"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11393280" y="75673080"/>
+          <a:ext cx="3809880" cy="2867040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4619880</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>2342880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Image 55" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="5182920"/>
+          <a:ext cx="4619880" cy="2342880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3990960</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>3286080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Image 56" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="10190520"/>
+          <a:ext cx="3990960" cy="3286080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4381560</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>3552840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Image 57" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="14340240"/>
+          <a:ext cx="4381560" cy="3552840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4791240</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>3295440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Image 58" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="18523080"/>
+          <a:ext cx="4791240" cy="3295440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4934160</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>3562200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Image 59" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="22704480"/>
+          <a:ext cx="4934160" cy="3562200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>252720</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>1647360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Image 60" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="27344520"/>
+          <a:ext cx="5400720" cy="1647360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4667400</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>2904840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Image 61" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="31233600"/>
+          <a:ext cx="4667400" cy="2904840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2800080</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>1009080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Image 62" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="35020080"/>
+          <a:ext cx="2800080" cy="1009080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2666880</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>961560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Image 63" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="36628560"/>
+          <a:ext cx="2666880" cy="961560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1962000</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>1009080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Image 64" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="38284200"/>
+          <a:ext cx="1962000" cy="1009080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2066760</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>1047240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="Image 65" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="39907800"/>
+          <a:ext cx="2066760" cy="1047240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3591000</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>4619880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Image 66" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="41585040"/>
+          <a:ext cx="3591000" cy="4619880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4324320</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>1723680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Image 67" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="47592000"/>
+          <a:ext cx="4324320" cy="1723680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3886200</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>3124080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Image 68" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="50184720"/>
+          <a:ext cx="3886200" cy="3124080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2076120</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>1037880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Image 69" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="54104400"/>
+          <a:ext cx="2076120" cy="1037880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1952280</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>990360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Image 70" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="55724400"/>
+          <a:ext cx="1952280" cy="990360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1495080</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>1047240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Image 71" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId17"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="57186720"/>
+          <a:ext cx="1495080" cy="1047240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3733920</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>3753000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Image 72" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="60222600"/>
+          <a:ext cx="3733920" cy="3753000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2228760</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>1161720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Image 73" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId19"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12946320" y="64564200"/>
+          <a:ext cx="2228760" cy="1161720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4653720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>2249280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Image 74" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="0"/>
+          <a:ext cx="4653720" cy="2249280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4962600</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1333080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Image 75" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="3051000"/>
+          <a:ext cx="4962600" cy="1333080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3605760</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>2369880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Image 76" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="5039280"/>
+          <a:ext cx="3605760" cy="2369880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3547800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>2229120</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Image 77" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="8327520"/>
+          <a:ext cx="3547800" cy="2229120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3876840</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1950480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Image 78" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="11866320"/>
+          <a:ext cx="3876840" cy="1950480"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4768560</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>2352600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Image 79" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="15996240"/>
+          <a:ext cx="4768560" cy="2352600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>6210720</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>2695320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Image 80" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="19566360"/>
+          <a:ext cx="6210720" cy="2695320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3381480</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>2657160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Image 81" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="23432040"/>
+          <a:ext cx="3381480" cy="2657160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4237200</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>3547440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Image 82" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="26826120"/>
+          <a:ext cx="4237200" cy="3547440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4934160</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>3162240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Image 83" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="31041360"/>
+          <a:ext cx="4934160" cy="3162240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5067360</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>1314000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Image 84" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="40404240"/>
+          <a:ext cx="5067360" cy="1314000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>7515720</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>2685960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Image 85" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="42555240"/>
+          <a:ext cx="7515720" cy="2685960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>6423840</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>2578320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Image 86" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="47332800"/>
+          <a:ext cx="6423840" cy="2578320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>6869880</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>2162160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Image 87" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="52162560"/>
+          <a:ext cx="6869880" cy="2162160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5322960</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>1681920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Image 88" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="55019520"/>
+          <a:ext cx="5322960" cy="1681920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5490000</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>2725200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Image 89" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="57208320"/>
+          <a:ext cx="5490000" cy="2725200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5671440</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>3115800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Image 90" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId17"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="60958800"/>
+          <a:ext cx="5671440" cy="3115800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4210200</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>3028680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Image 91" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="65869920"/>
+          <a:ext cx="4210200" cy="3028680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3467160</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>3657600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Image 92" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId19"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="70114680"/>
+          <a:ext cx="3467160" cy="3657600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2466720</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>799560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Image 93" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId20"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="75887640"/>
+          <a:ext cx="2466720" cy="799560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2943000</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>742680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Image 94" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId21"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="77491440"/>
+          <a:ext cx="2943000" cy="742680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3305160</xdr:colOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>809280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Image 95" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId22"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11557080" y="78701400"/>
+          <a:ext cx="3305160" cy="809280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5477040</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>2523960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Image 96" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10870560" y="0"/>
+          <a:ext cx="5477040" cy="2523960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4229280</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>2590560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Image 97" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10870560" y="3198960"/>
+          <a:ext cx="4229280" cy="2590560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4734000</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>2876400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Image 98" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10870560" y="6985800"/>
+          <a:ext cx="4734000" cy="2876400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5495760</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>3008160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Image 99" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10870560" y="12856320"/>
+          <a:ext cx="5495760" cy="3008160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5268600</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>1728720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Image 100" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10870560" y="17430840"/>
+          <a:ext cx="5268600" cy="1728720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4819680</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>8001720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Image 101" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10870560" y="19750320"/>
+          <a:ext cx="4819680" cy="8001720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3019320</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>1504800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Image 102" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10870560" y="28241640"/>
+          <a:ext cx="3019320" cy="1504800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5286600</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>2562120</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Image 103" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10870560" y="30823560"/>
+          <a:ext cx="5286600" cy="2562120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -876,7 +5823,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A91"/>
+  <dimension ref="A1:A177"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="60.75"/>
@@ -1230,6 +6177,2611 @@
         <v>68</v>
       </c>
     </row>
+    <row r="95" customFormat="false" ht="68.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="176.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="317.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="319.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="232.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="144.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A175" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="155.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A177" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A133"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="87.18"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="67.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="4" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="131.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="57.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="205.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="253.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="398" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="254.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="226.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="72.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="124.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="79.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="358.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="110.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="359.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A132"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="80.92"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="88.11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="4" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="110.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="62.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="247.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="384.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="166.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="190.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="195.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="271.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="108.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="195.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="216.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="226.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="171.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="206.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="186.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="246.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="245" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="262.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="313.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="245" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A118"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="102.96"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="73.04"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="4" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6"/>
+    </row>
+    <row r="23" customFormat="false" ht="190.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6"/>
+    </row>
+    <row r="35" customFormat="false" ht="271.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="292.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="273.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="309.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6"/>
+    </row>
+    <row r="49" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6"/>
+    </row>
+    <row r="50" customFormat="false" ht="139.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6"/>
+    </row>
+    <row r="59" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6"/>
+    </row>
+    <row r="63" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6"/>
+    </row>
+    <row r="64" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="6"/>
+    </row>
+    <row r="67" customFormat="false" ht="93.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="6"/>
+    </row>
+    <row r="70" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="6"/>
+    </row>
+    <row r="72" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="6"/>
+    </row>
+    <row r="73" customFormat="false" ht="100.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="370.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="152.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="257.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="101.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="98.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="303.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="110.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A185"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="83.24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="112.23"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="4" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="189.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="118.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="207.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="189.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="171.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="191.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="227.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="228.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="293.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="263.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="118.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="222.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="213.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="186.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="146.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="258.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="4" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="4" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="257.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="300.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="4" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="4" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="100.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A173" s="4" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="69.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A177" s="4" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="95.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A180" s="4" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A69"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="73.51"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="83.24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="4" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="210.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="221.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="257.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="245" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="144.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="643" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="139.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="213.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>534</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/src/main/resources/espacios/software/Java OPP.xlsx
+++ b/src/main/resources/espacios/software/Java OPP.xlsx
@@ -1639,7 +1639,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1666,11 +1666,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="15"/>
@@ -1727,7 +1722,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1744,15 +1739,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1779,9 +1766,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3256920</xdr:colOff>
+      <xdr:colOff>3256560</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>2237400</xdr:rowOff>
+      <xdr:rowOff>2237040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1795,7 +1782,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="4064040"/>
-          <a:ext cx="3256920" cy="2237400"/>
+          <a:ext cx="3256560" cy="2237040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1817,9 +1804,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3542400</xdr:colOff>
+      <xdr:colOff>3542040</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>1675440</xdr:rowOff>
+      <xdr:rowOff>1675080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1833,7 +1820,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="7555320"/>
-          <a:ext cx="3542400" cy="1675440"/>
+          <a:ext cx="3542040" cy="1675080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1855,9 +1842,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3304440</xdr:colOff>
+      <xdr:colOff>3304080</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>2256480</xdr:rowOff>
+      <xdr:rowOff>2256120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1871,7 +1858,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="10137240"/>
-          <a:ext cx="3304440" cy="2256480"/>
+          <a:ext cx="3304080" cy="2256120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1893,9 +1880,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2971080</xdr:colOff>
+      <xdr:colOff>2970720</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>2446920</xdr:rowOff>
+      <xdr:rowOff>2446560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1909,7 +1896,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="13497480"/>
-          <a:ext cx="2971080" cy="2446920"/>
+          <a:ext cx="2970720" cy="2446560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1931,9 +1918,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3047040</xdr:colOff>
+      <xdr:colOff>3046680</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>2437560</xdr:rowOff>
+      <xdr:rowOff>2437200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1947,7 +1934,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="16527960"/>
-          <a:ext cx="3047040" cy="2437560"/>
+          <a:ext cx="3046680" cy="2437200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1969,9 +1956,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>697320</xdr:colOff>
+      <xdr:colOff>696960</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>2199240</xdr:rowOff>
+      <xdr:rowOff>2198880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1985,7 +1972,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="19296360"/>
-          <a:ext cx="5373000" cy="2199240"/>
+          <a:ext cx="5373360" cy="2198880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2007,9 +1994,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4361760</xdr:colOff>
+      <xdr:colOff>4361400</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>2761200</xdr:rowOff>
+      <xdr:rowOff>2760840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2023,7 +2010,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="22299840"/>
-          <a:ext cx="4361760" cy="2761200"/>
+          <a:ext cx="4361400" cy="2760840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2045,9 +2032,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4209480</xdr:colOff>
+      <xdr:colOff>4209120</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>2485080</xdr:rowOff>
+      <xdr:rowOff>2484720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2061,7 +2048,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="25809120"/>
-          <a:ext cx="4209480" cy="2485080"/>
+          <a:ext cx="4209120" cy="2484720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2083,9 +2070,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4175640</xdr:colOff>
+      <xdr:colOff>4175280</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>3413160</xdr:rowOff>
+      <xdr:rowOff>3412800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2099,7 +2086,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="28771920"/>
-          <a:ext cx="4175640" cy="3413160"/>
+          <a:ext cx="4175280" cy="3412800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2121,9 +2108,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4116600</xdr:colOff>
+      <xdr:colOff>4116240</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>2176920</xdr:rowOff>
+      <xdr:rowOff>2176560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2137,7 +2124,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="33348240"/>
-          <a:ext cx="4116600" cy="2176920"/>
+          <a:ext cx="4116240" cy="2176560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2159,9 +2146,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4152960</xdr:colOff>
+      <xdr:colOff>4152600</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>2838240</xdr:rowOff>
+      <xdr:rowOff>2837880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2175,7 +2162,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="37668240"/>
-          <a:ext cx="4152960" cy="2838240"/>
+          <a:ext cx="4152600" cy="2837880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2197,9 +2184,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1561680</xdr:colOff>
+      <xdr:colOff>1561320</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>780480</xdr:rowOff>
+      <xdr:rowOff>780120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2213,7 +2200,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="41953680"/>
-          <a:ext cx="1561680" cy="780480"/>
+          <a:ext cx="1561320" cy="780120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2235,9 +2222,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>811080</xdr:colOff>
+      <xdr:colOff>810720</xdr:colOff>
       <xdr:row>139</xdr:row>
-      <xdr:rowOff>2095200</xdr:rowOff>
+      <xdr:rowOff>2094840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2251,7 +2238,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="49975200"/>
-          <a:ext cx="5486760" cy="2095200"/>
+          <a:ext cx="5487120" cy="2094840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2273,9 +2260,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>2160</xdr:colOff>
+      <xdr:colOff>1800</xdr:colOff>
       <xdr:row>144</xdr:row>
-      <xdr:rowOff>3476160</xdr:rowOff>
+      <xdr:rowOff>3475800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2289,7 +2276,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="52868160"/>
-          <a:ext cx="4677840" cy="3476160"/>
+          <a:ext cx="4678200" cy="3475800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2311,9 +2298,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4572360</xdr:colOff>
+      <xdr:colOff>4572000</xdr:colOff>
       <xdr:row>149</xdr:row>
-      <xdr:rowOff>3920040</xdr:rowOff>
+      <xdr:rowOff>3919680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2327,7 +2314,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="57546360"/>
-          <a:ext cx="4572360" cy="3920040"/>
+          <a:ext cx="4572000" cy="3919680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2349,9 +2336,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3647880</xdr:colOff>
+      <xdr:colOff>3647520</xdr:colOff>
       <xdr:row>162</xdr:row>
-      <xdr:rowOff>2790720</xdr:rowOff>
+      <xdr:rowOff>2790360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2365,7 +2352,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="63556560"/>
-          <a:ext cx="3647880" cy="2790720"/>
+          <a:ext cx="3647520" cy="2790360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2387,9 +2374,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2952720</xdr:colOff>
+      <xdr:colOff>2952360</xdr:colOff>
       <xdr:row>174</xdr:row>
-      <xdr:rowOff>1523520</xdr:rowOff>
+      <xdr:rowOff>1523160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2403,7 +2390,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="68298120"/>
-          <a:ext cx="2952720" cy="1523520"/>
+          <a:ext cx="2952360" cy="1523160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2425,9 +2412,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>20160</xdr:colOff>
+      <xdr:colOff>19800</xdr:colOff>
       <xdr:row>176</xdr:row>
-      <xdr:rowOff>1780920</xdr:rowOff>
+      <xdr:rowOff>1780560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2441,7 +2428,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9971280" y="70292520"/>
-          <a:ext cx="4695840" cy="1780920"/>
+          <a:ext cx="4696200" cy="1780560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2468,9 +2455,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3790800</xdr:colOff>
+      <xdr:colOff>3790440</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>1447560</xdr:rowOff>
+      <xdr:rowOff>1447200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2484,7 +2471,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="1300320"/>
-          <a:ext cx="3790800" cy="1447560"/>
+          <a:ext cx="3790440" cy="1447200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2506,9 +2493,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1952280</xdr:colOff>
+      <xdr:colOff>1951920</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>580680</xdr:rowOff>
+      <xdr:rowOff>580320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2522,7 +2509,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="4600080"/>
-          <a:ext cx="1952280" cy="580680"/>
+          <a:ext cx="1951920" cy="580320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2544,9 +2531,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4646520</xdr:colOff>
+      <xdr:colOff>4646160</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>2409840</xdr:rowOff>
+      <xdr:rowOff>2409480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2560,7 +2547,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="6951960"/>
-          <a:ext cx="4646520" cy="2409840"/>
+          <a:ext cx="4646160" cy="2409480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2582,9 +2569,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3676680</xdr:colOff>
+      <xdr:colOff>3676320</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>3076560</xdr:rowOff>
+      <xdr:rowOff>3076200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2598,7 +2585,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="12321720"/>
-          <a:ext cx="3676680" cy="3076560"/>
+          <a:ext cx="3676320" cy="3076200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2620,9 +2607,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4095720</xdr:colOff>
+      <xdr:colOff>4095360</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>4886640</xdr:rowOff>
+      <xdr:rowOff>4886280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2636,7 +2623,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="17006400"/>
-          <a:ext cx="4095720" cy="4886640"/>
+          <a:ext cx="4095360" cy="4886280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2658,9 +2645,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4067280</xdr:colOff>
+      <xdr:colOff>4066920</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>3143160</xdr:rowOff>
+      <xdr:rowOff>3142800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2674,7 +2661,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="22874040"/>
-          <a:ext cx="4067280" cy="3143160"/>
+          <a:ext cx="4066920" cy="3142800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2696,9 +2683,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4362480</xdr:colOff>
+      <xdr:colOff>4362120</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>2743200</xdr:rowOff>
+      <xdr:rowOff>2742840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2712,7 +2699,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="27412200"/>
-          <a:ext cx="4362480" cy="2743200"/>
+          <a:ext cx="4362120" cy="2742840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2734,9 +2721,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>200520</xdr:colOff>
+      <xdr:colOff>200160</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>685440</xdr:rowOff>
+      <xdr:rowOff>685080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2750,7 +2737,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="30774600"/>
-          <a:ext cx="4972320" cy="685440"/>
+          <a:ext cx="4971960" cy="685080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2772,9 +2759,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2609640</xdr:colOff>
+      <xdr:colOff>2609280</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>1399680</xdr:rowOff>
+      <xdr:rowOff>1399320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2788,7 +2775,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="32340600"/>
-          <a:ext cx="2609640" cy="1399680"/>
+          <a:ext cx="2609280" cy="1399320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2810,9 +2797,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3933720</xdr:colOff>
+      <xdr:colOff>3933360</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>847440</xdr:rowOff>
+      <xdr:rowOff>847080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2826,7 +2813,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="35545320"/>
-          <a:ext cx="3933720" cy="847440"/>
+          <a:ext cx="3933360" cy="847080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2848,9 +2835,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3209760</xdr:colOff>
+      <xdr:colOff>3209400</xdr:colOff>
       <xdr:row>97</xdr:row>
-      <xdr:rowOff>4334040</xdr:rowOff>
+      <xdr:rowOff>4333680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2864,7 +2851,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="37044000"/>
-          <a:ext cx="3209760" cy="4334040"/>
+          <a:ext cx="3209400" cy="4333680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2886,9 +2873,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4667400</xdr:colOff>
+      <xdr:colOff>4667040</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>1171080</xdr:rowOff>
+      <xdr:rowOff>1170720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2902,7 +2889,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="43056000"/>
-          <a:ext cx="4667400" cy="1171080"/>
+          <a:ext cx="4667040" cy="1170720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2924,9 +2911,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4524480</xdr:colOff>
+      <xdr:colOff>4524120</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>4390920</xdr:rowOff>
+      <xdr:rowOff>4390560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2940,7 +2927,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11834640" y="45436680"/>
-          <a:ext cx="4524480" cy="4390920"/>
+          <a:ext cx="4524120" cy="4390560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2967,9 +2954,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1514160</xdr:colOff>
+      <xdr:colOff>1513800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1161720</xdr:rowOff>
+      <xdr:rowOff>1161360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2983,7 +2970,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="0"/>
-          <a:ext cx="1514160" cy="1161720"/>
+          <a:ext cx="1513800" cy="1161360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3005,9 +2992,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2523960</xdr:colOff>
+      <xdr:colOff>2523600</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>590040</xdr:rowOff>
+      <xdr:rowOff>589680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3021,7 +3008,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="2055600"/>
-          <a:ext cx="2523960" cy="590040"/>
+          <a:ext cx="2523600" cy="589680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3043,9 +3030,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3000240</xdr:colOff>
+      <xdr:colOff>2999880</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>2971800</xdr:rowOff>
+      <xdr:rowOff>2971440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3059,7 +3046,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="3494880"/>
-          <a:ext cx="3000240" cy="2971800"/>
+          <a:ext cx="2999880" cy="2971440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3081,9 +3068,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3095640</xdr:colOff>
+      <xdr:colOff>3095280</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>4695840</xdr:rowOff>
+      <xdr:rowOff>4695480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3097,7 +3084,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="7288560"/>
-          <a:ext cx="3095640" cy="4695840"/>
+          <a:ext cx="3095280" cy="4695480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3119,9 +3106,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2571480</xdr:colOff>
+      <xdr:colOff>2571120</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1876320</xdr:rowOff>
+      <xdr:rowOff>1875960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3135,7 +3122,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="12819240"/>
-          <a:ext cx="2571480" cy="1876320"/>
+          <a:ext cx="2571120" cy="1875960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3157,9 +3144,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4048200</xdr:colOff>
+      <xdr:colOff>4047840</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>2352600</xdr:rowOff>
+      <xdr:rowOff>2352240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3173,7 +3160,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="18999720"/>
-          <a:ext cx="4048200" cy="2352600"/>
+          <a:ext cx="4047840" cy="2352240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3195,9 +3182,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4734000</xdr:colOff>
+      <xdr:colOff>4733640</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>2247840</xdr:rowOff>
+      <xdr:rowOff>2247480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3211,7 +3198,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="22696200"/>
-          <a:ext cx="4734000" cy="2247840"/>
+          <a:ext cx="4733640" cy="2247480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3233,9 +3220,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4200480</xdr:colOff>
+      <xdr:colOff>4200120</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>2285640</xdr:rowOff>
+      <xdr:rowOff>2285280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3249,7 +3236,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="25599960"/>
-          <a:ext cx="4200480" cy="2285640"/>
+          <a:ext cx="4200120" cy="2285280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3271,9 +3258,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5457960</xdr:colOff>
+      <xdr:colOff>5457600</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>3276360</xdr:rowOff>
+      <xdr:rowOff>3276000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3287,7 +3274,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="28892520"/>
-          <a:ext cx="5457960" cy="3276360"/>
+          <a:ext cx="5457600" cy="3276000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3309,9 +3296,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3390840</xdr:colOff>
+      <xdr:colOff>3390480</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>1695240</xdr:rowOff>
+      <xdr:rowOff>1694880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3325,7 +3312,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="33310800"/>
-          <a:ext cx="3390840" cy="1695240"/>
+          <a:ext cx="3390480" cy="1694880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3347,9 +3334,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5210280</xdr:colOff>
+      <xdr:colOff>5209920</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>1209240</xdr:rowOff>
+      <xdr:rowOff>1208880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3363,7 +3350,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="35546760"/>
-          <a:ext cx="5210280" cy="1209240"/>
+          <a:ext cx="5209920" cy="1208880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3385,9 +3372,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3476520</xdr:colOff>
+      <xdr:colOff>3476160</xdr:colOff>
       <xdr:row>83</xdr:row>
-      <xdr:rowOff>2314440</xdr:rowOff>
+      <xdr:rowOff>2314080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3401,7 +3388,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="38221200"/>
-          <a:ext cx="3476520" cy="2314440"/>
+          <a:ext cx="3476160" cy="2314080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3423,9 +3410,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4810320</xdr:colOff>
+      <xdr:colOff>4809960</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>2600280</xdr:rowOff>
+      <xdr:rowOff>2599920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3439,7 +3426,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="41188680"/>
-          <a:ext cx="4810320" cy="2600280"/>
+          <a:ext cx="4809960" cy="2599920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3461,9 +3448,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3909960</xdr:colOff>
+      <xdr:colOff>3909600</xdr:colOff>
       <xdr:row>91</xdr:row>
-      <xdr:rowOff>2669400</xdr:rowOff>
+      <xdr:rowOff>2669040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3477,7 +3464,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="44424720"/>
-          <a:ext cx="3909960" cy="2669400"/>
+          <a:ext cx="3909600" cy="2669040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3499,9 +3486,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3954600</xdr:colOff>
+      <xdr:colOff>3954240</xdr:colOff>
       <xdr:row>95</xdr:row>
-      <xdr:rowOff>2019600</xdr:rowOff>
+      <xdr:rowOff>2019240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3515,7 +3502,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="47786760"/>
-          <a:ext cx="3954600" cy="2019600"/>
+          <a:ext cx="3954240" cy="2019240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3537,9 +3524,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3959280</xdr:colOff>
+      <xdr:colOff>3958920</xdr:colOff>
       <xdr:row>98</xdr:row>
-      <xdr:rowOff>2449440</xdr:rowOff>
+      <xdr:rowOff>2449080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3553,7 +3540,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="50291280"/>
-          <a:ext cx="3959280" cy="2449440"/>
+          <a:ext cx="3958920" cy="2449080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3575,9 +3562,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3918240</xdr:colOff>
+      <xdr:colOff>3917880</xdr:colOff>
       <xdr:row>101</xdr:row>
-      <xdr:rowOff>2630520</xdr:rowOff>
+      <xdr:rowOff>2630160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3591,7 +3578,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="53238240"/>
-          <a:ext cx="3918240" cy="2630520"/>
+          <a:ext cx="3917880" cy="2630160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3613,9 +3600,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4008960</xdr:colOff>
+      <xdr:colOff>4008600</xdr:colOff>
       <xdr:row>104</xdr:row>
-      <xdr:rowOff>2221920</xdr:rowOff>
+      <xdr:rowOff>2221560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3629,7 +3616,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="56500920"/>
-          <a:ext cx="4008960" cy="2221920"/>
+          <a:ext cx="4008600" cy="2221560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3651,9 +3638,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4730400</xdr:colOff>
+      <xdr:colOff>4730040</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>2971440</xdr:rowOff>
+      <xdr:rowOff>2971080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3667,7 +3654,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="59195160"/>
-          <a:ext cx="4730400" cy="2971440"/>
+          <a:ext cx="4730040" cy="2971080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3689,9 +3676,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4286160</xdr:colOff>
+      <xdr:colOff>4285800</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>2923920</xdr:rowOff>
+      <xdr:rowOff>2923560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3705,7 +3692,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="63298080"/>
-          <a:ext cx="4286160" cy="2923920"/>
+          <a:ext cx="4285800" cy="2923560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3727,9 +3714,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4029120</xdr:colOff>
+      <xdr:colOff>4028760</xdr:colOff>
       <xdr:row>122</xdr:row>
-      <xdr:rowOff>3200400</xdr:rowOff>
+      <xdr:rowOff>3200040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3743,7 +3730,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="67547520"/>
-          <a:ext cx="4029120" cy="3200400"/>
+          <a:ext cx="4028760" cy="3200040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3765,9 +3752,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3943440</xdr:colOff>
+      <xdr:colOff>3943080</xdr:colOff>
       <xdr:row>126</xdr:row>
-      <xdr:rowOff>3591000</xdr:rowOff>
+      <xdr:rowOff>3590640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3781,7 +3768,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="71367480"/>
-          <a:ext cx="3943440" cy="3591000"/>
+          <a:ext cx="3943080" cy="3590640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3803,9 +3790,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3809880</xdr:colOff>
+      <xdr:colOff>3809520</xdr:colOff>
       <xdr:row>129</xdr:row>
-      <xdr:rowOff>2867040</xdr:rowOff>
+      <xdr:rowOff>2866680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3819,7 +3806,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11393280" y="75673080"/>
-          <a:ext cx="3809880" cy="2867040"/>
+          <a:ext cx="3809520" cy="2866680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3846,9 +3833,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4619880</xdr:colOff>
+      <xdr:colOff>4619520</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>2342880</xdr:rowOff>
+      <xdr:rowOff>2342520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3861,8 +3848,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="5182920"/>
-          <a:ext cx="4619880" cy="2342880"/>
+          <a:off x="12947040" y="5182920"/>
+          <a:ext cx="4619520" cy="2342520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3884,9 +3871,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3990960</xdr:colOff>
+      <xdr:colOff>3990600</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>3286080</xdr:rowOff>
+      <xdr:rowOff>3285720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3899,8 +3886,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="10190520"/>
-          <a:ext cx="3990960" cy="3286080"/>
+          <a:off x="12947040" y="10190520"/>
+          <a:ext cx="3990600" cy="3285720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3922,9 +3909,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4381560</xdr:colOff>
+      <xdr:colOff>4381200</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>3552840</xdr:rowOff>
+      <xdr:rowOff>3552480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3937,8 +3924,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="14340240"/>
-          <a:ext cx="4381560" cy="3552840"/>
+          <a:off x="12947040" y="14340240"/>
+          <a:ext cx="4381200" cy="3552480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3960,9 +3947,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4791240</xdr:colOff>
+      <xdr:colOff>4790880</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>3295440</xdr:rowOff>
+      <xdr:rowOff>3295080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3975,8 +3962,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="18523080"/>
-          <a:ext cx="4791240" cy="3295440"/>
+          <a:off x="12947040" y="18523080"/>
+          <a:ext cx="4790880" cy="3295080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3998,9 +3985,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4934160</xdr:colOff>
+      <xdr:colOff>4933800</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>3562200</xdr:rowOff>
+      <xdr:rowOff>3561840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4013,8 +4000,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="22704480"/>
-          <a:ext cx="4934160" cy="3562200"/>
+          <a:off x="12947040" y="22704480"/>
+          <a:ext cx="4933800" cy="3561840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4036,9 +4023,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>252720</xdr:colOff>
+      <xdr:colOff>252360</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>1647360</xdr:rowOff>
+      <xdr:rowOff>1647000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4051,8 +4038,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="27344520"/>
-          <a:ext cx="5400720" cy="1647360"/>
+          <a:off x="12947040" y="27344520"/>
+          <a:ext cx="5400360" cy="1647000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4074,9 +4061,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4667400</xdr:colOff>
+      <xdr:colOff>4667040</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>2904840</xdr:rowOff>
+      <xdr:rowOff>2904480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4089,8 +4076,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="31233600"/>
-          <a:ext cx="4667400" cy="2904840"/>
+          <a:off x="12947040" y="31233600"/>
+          <a:ext cx="4667040" cy="2904480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4112,9 +4099,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2800080</xdr:colOff>
+      <xdr:colOff>2799720</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>1009080</xdr:rowOff>
+      <xdr:rowOff>1008720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4127,8 +4114,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="35020080"/>
-          <a:ext cx="2800080" cy="1009080"/>
+          <a:off x="12947040" y="35020080"/>
+          <a:ext cx="2799720" cy="1008720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4150,9 +4137,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2666880</xdr:colOff>
+      <xdr:colOff>2666520</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>961560</xdr:rowOff>
+      <xdr:rowOff>961200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4165,8 +4152,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="36628560"/>
-          <a:ext cx="2666880" cy="961560"/>
+          <a:off x="12947040" y="36628560"/>
+          <a:ext cx="2666520" cy="961200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4188,9 +4175,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1962000</xdr:colOff>
+      <xdr:colOff>1961640</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>1009080</xdr:rowOff>
+      <xdr:rowOff>1008720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4203,8 +4190,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="38284200"/>
-          <a:ext cx="1962000" cy="1009080"/>
+          <a:off x="12947040" y="38284200"/>
+          <a:ext cx="1961640" cy="1008720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4226,9 +4213,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2066760</xdr:colOff>
+      <xdr:colOff>2066400</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>1047240</xdr:rowOff>
+      <xdr:rowOff>1046880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4241,8 +4228,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="39907800"/>
-          <a:ext cx="2066760" cy="1047240"/>
+          <a:off x="12947040" y="39907800"/>
+          <a:ext cx="2066400" cy="1046880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4264,9 +4251,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3591000</xdr:colOff>
+      <xdr:colOff>3590640</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>4619880</xdr:rowOff>
+      <xdr:rowOff>4619520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4279,8 +4266,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="41585040"/>
-          <a:ext cx="3591000" cy="4619880"/>
+          <a:off x="12947040" y="41585040"/>
+          <a:ext cx="3590640" cy="4619520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4302,9 +4289,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4324320</xdr:colOff>
+      <xdr:colOff>4323960</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>1723680</xdr:rowOff>
+      <xdr:rowOff>1723320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4317,8 +4304,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="47592000"/>
-          <a:ext cx="4324320" cy="1723680"/>
+          <a:off x="12947040" y="47592000"/>
+          <a:ext cx="4323960" cy="1723320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4340,9 +4327,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3886200</xdr:colOff>
+      <xdr:colOff>3885840</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>3124080</xdr:rowOff>
+      <xdr:rowOff>3123720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4355,8 +4342,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="50184720"/>
-          <a:ext cx="3886200" cy="3124080"/>
+          <a:off x="12947040" y="50184720"/>
+          <a:ext cx="3885840" cy="3123720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4378,9 +4365,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2076120</xdr:colOff>
+      <xdr:colOff>2075760</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>1037880</xdr:rowOff>
+      <xdr:rowOff>1037520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4393,8 +4380,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="54104400"/>
-          <a:ext cx="2076120" cy="1037880"/>
+          <a:off x="12947040" y="54104400"/>
+          <a:ext cx="2075760" cy="1037520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4416,9 +4403,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1952280</xdr:colOff>
+      <xdr:colOff>1951920</xdr:colOff>
       <xdr:row>97</xdr:row>
-      <xdr:rowOff>990360</xdr:rowOff>
+      <xdr:rowOff>990000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4431,8 +4418,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="55724400"/>
-          <a:ext cx="1952280" cy="990360"/>
+          <a:off x="12947040" y="55724400"/>
+          <a:ext cx="1951920" cy="990000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4454,9 +4441,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1495080</xdr:colOff>
+      <xdr:colOff>1494720</xdr:colOff>
       <xdr:row>100</xdr:row>
-      <xdr:rowOff>1047240</xdr:rowOff>
+      <xdr:rowOff>1046880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4469,8 +4456,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="57186720"/>
-          <a:ext cx="1495080" cy="1047240"/>
+          <a:off x="12947040" y="57186720"/>
+          <a:ext cx="1494720" cy="1046880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4492,9 +4479,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3733920</xdr:colOff>
+      <xdr:colOff>3733560</xdr:colOff>
       <xdr:row>112</xdr:row>
-      <xdr:rowOff>3753000</xdr:rowOff>
+      <xdr:rowOff>3752640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4507,8 +4494,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="60222600"/>
-          <a:ext cx="3733920" cy="3753000"/>
+          <a:off x="12947040" y="60222600"/>
+          <a:ext cx="3733560" cy="3752640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4530,9 +4517,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2228760</xdr:colOff>
+      <xdr:colOff>2228400</xdr:colOff>
       <xdr:row>116</xdr:row>
-      <xdr:rowOff>1161720</xdr:rowOff>
+      <xdr:rowOff>1161360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4545,8 +4532,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12946320" y="64564200"/>
-          <a:ext cx="2228760" cy="1161720"/>
+          <a:off x="12947040" y="64564200"/>
+          <a:ext cx="2228400" cy="1161360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4573,9 +4560,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4653720</xdr:colOff>
+      <xdr:colOff>4653360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2249280</xdr:rowOff>
+      <xdr:rowOff>2248920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4589,7 +4576,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="0"/>
-          <a:ext cx="4653720" cy="2249280"/>
+          <a:ext cx="4653360" cy="2248920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4611,9 +4598,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4962600</xdr:colOff>
+      <xdr:colOff>4962240</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1333080</xdr:rowOff>
+      <xdr:rowOff>1332720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4627,7 +4614,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="3051000"/>
-          <a:ext cx="4962600" cy="1333080"/>
+          <a:ext cx="4962240" cy="1332720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4649,9 +4636,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3605760</xdr:colOff>
+      <xdr:colOff>3605400</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>2369880</xdr:rowOff>
+      <xdr:rowOff>2369520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4665,7 +4652,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="5039280"/>
-          <a:ext cx="3605760" cy="2369880"/>
+          <a:ext cx="3605400" cy="2369520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4687,9 +4674,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3547800</xdr:colOff>
+      <xdr:colOff>3547440</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>2229120</xdr:rowOff>
+      <xdr:rowOff>2228760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4703,7 +4690,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="8327520"/>
-          <a:ext cx="3547800" cy="2229120"/>
+          <a:ext cx="3547440" cy="2228760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4725,9 +4712,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3876840</xdr:colOff>
+      <xdr:colOff>3876480</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>1950480</xdr:rowOff>
+      <xdr:rowOff>1950120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4741,7 +4728,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="11866320"/>
-          <a:ext cx="3876840" cy="1950480"/>
+          <a:ext cx="3876480" cy="1950120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4763,9 +4750,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4768560</xdr:colOff>
+      <xdr:colOff>4768200</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>2352600</xdr:rowOff>
+      <xdr:rowOff>2352240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4779,7 +4766,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="15996240"/>
-          <a:ext cx="4768560" cy="2352600"/>
+          <a:ext cx="4768200" cy="2352240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4801,9 +4788,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>6210720</xdr:colOff>
+      <xdr:colOff>6210360</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>2695320</xdr:rowOff>
+      <xdr:rowOff>2694960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4817,7 +4804,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="19566360"/>
-          <a:ext cx="6210720" cy="2695320"/>
+          <a:ext cx="6210360" cy="2694960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4839,9 +4826,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3381480</xdr:colOff>
+      <xdr:colOff>3381120</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>2657160</xdr:rowOff>
+      <xdr:rowOff>2656800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4855,7 +4842,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="23432040"/>
-          <a:ext cx="3381480" cy="2657160"/>
+          <a:ext cx="3381120" cy="2656800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4877,9 +4864,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4237200</xdr:colOff>
+      <xdr:colOff>4236840</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>3547440</xdr:rowOff>
+      <xdr:rowOff>3547080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4893,7 +4880,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="26826120"/>
-          <a:ext cx="4237200" cy="3547440"/>
+          <a:ext cx="4236840" cy="3547080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4915,9 +4902,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4934160</xdr:colOff>
+      <xdr:colOff>4933800</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>3162240</xdr:rowOff>
+      <xdr:rowOff>3161880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4931,7 +4918,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="31041360"/>
-          <a:ext cx="4934160" cy="3162240"/>
+          <a:ext cx="4933800" cy="3161880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4953,9 +4940,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5067360</xdr:colOff>
+      <xdr:colOff>5067000</xdr:colOff>
       <xdr:row>96</xdr:row>
-      <xdr:rowOff>1314000</xdr:rowOff>
+      <xdr:rowOff>1313640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4969,7 +4956,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="40404240"/>
-          <a:ext cx="5067360" cy="1314000"/>
+          <a:ext cx="5067000" cy="1313640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4991,9 +4978,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>7515720</xdr:colOff>
+      <xdr:colOff>7515360</xdr:colOff>
       <xdr:row>101</xdr:row>
-      <xdr:rowOff>2685960</xdr:rowOff>
+      <xdr:rowOff>2685600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5007,7 +4994,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="42555240"/>
-          <a:ext cx="7515720" cy="2685960"/>
+          <a:ext cx="7515360" cy="2685600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5029,9 +5016,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>6423840</xdr:colOff>
+      <xdr:colOff>6423480</xdr:colOff>
       <xdr:row>114</xdr:row>
-      <xdr:rowOff>2578320</xdr:rowOff>
+      <xdr:rowOff>2577960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5045,7 +5032,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="47332800"/>
-          <a:ext cx="6423840" cy="2578320"/>
+          <a:ext cx="6423480" cy="2577960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5067,9 +5054,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>6869880</xdr:colOff>
+      <xdr:colOff>6869520</xdr:colOff>
       <xdr:row>128</xdr:row>
-      <xdr:rowOff>2162160</xdr:rowOff>
+      <xdr:rowOff>2161800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5083,7 +5070,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="52162560"/>
-          <a:ext cx="6869880" cy="2162160"/>
+          <a:ext cx="6869520" cy="2161800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5105,9 +5092,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5322960</xdr:colOff>
+      <xdr:colOff>5322600</xdr:colOff>
       <xdr:row>132</xdr:row>
-      <xdr:rowOff>1681920</xdr:rowOff>
+      <xdr:rowOff>1681560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5121,7 +5108,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="55019520"/>
-          <a:ext cx="5322960" cy="1681920"/>
+          <a:ext cx="5322600" cy="1681560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5143,9 +5130,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5490000</xdr:colOff>
+      <xdr:colOff>5489640</xdr:colOff>
       <xdr:row>135</xdr:row>
-      <xdr:rowOff>2725200</xdr:rowOff>
+      <xdr:rowOff>2724840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5159,7 +5146,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="57208320"/>
-          <a:ext cx="5490000" cy="2725200"/>
+          <a:ext cx="5489640" cy="2724840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5181,9 +5168,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5671440</xdr:colOff>
+      <xdr:colOff>5671080</xdr:colOff>
       <xdr:row>141</xdr:row>
-      <xdr:rowOff>3115800</xdr:rowOff>
+      <xdr:rowOff>3115440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5197,7 +5184,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="60958800"/>
-          <a:ext cx="5671440" cy="3115800"/>
+          <a:ext cx="5671080" cy="3115440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5219,9 +5206,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4210200</xdr:colOff>
+      <xdr:colOff>4209840</xdr:colOff>
       <xdr:row>152</xdr:row>
-      <xdr:rowOff>3028680</xdr:rowOff>
+      <xdr:rowOff>3028320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5235,7 +5222,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="65869920"/>
-          <a:ext cx="4210200" cy="3028680"/>
+          <a:ext cx="4209840" cy="3028320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5257,9 +5244,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3467160</xdr:colOff>
+      <xdr:colOff>3466800</xdr:colOff>
       <xdr:row>159</xdr:row>
-      <xdr:rowOff>3657600</xdr:rowOff>
+      <xdr:rowOff>3657240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5273,7 +5260,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="70114680"/>
-          <a:ext cx="3467160" cy="3657600"/>
+          <a:ext cx="3466800" cy="3657240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5295,9 +5282,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2466720</xdr:colOff>
+      <xdr:colOff>2466360</xdr:colOff>
       <xdr:row>172</xdr:row>
-      <xdr:rowOff>799560</xdr:rowOff>
+      <xdr:rowOff>799200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5311,7 +5298,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="75887640"/>
-          <a:ext cx="2466720" cy="799560"/>
+          <a:ext cx="2466360" cy="799200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5333,9 +5320,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2943000</xdr:colOff>
+      <xdr:colOff>2942640</xdr:colOff>
       <xdr:row>176</xdr:row>
-      <xdr:rowOff>742680</xdr:rowOff>
+      <xdr:rowOff>742320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5349,7 +5336,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="77491440"/>
-          <a:ext cx="2943000" cy="742680"/>
+          <a:ext cx="2942640" cy="742320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5371,9 +5358,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3305160</xdr:colOff>
+      <xdr:colOff>3304800</xdr:colOff>
       <xdr:row>179</xdr:row>
-      <xdr:rowOff>809280</xdr:rowOff>
+      <xdr:rowOff>808920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5387,7 +5374,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11557080" y="78701400"/>
-          <a:ext cx="3305160" cy="809280"/>
+          <a:ext cx="3304800" cy="808920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5414,9 +5401,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5477040</xdr:colOff>
+      <xdr:colOff>5476680</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2523960</xdr:rowOff>
+      <xdr:rowOff>2523600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5429,8 +5416,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10870560" y="0"/>
-          <a:ext cx="5477040" cy="2523960"/>
+          <a:off x="10871280" y="0"/>
+          <a:ext cx="5476680" cy="2523600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5452,9 +5439,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4229280</xdr:colOff>
+      <xdr:colOff>4228920</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>2590560</xdr:rowOff>
+      <xdr:rowOff>2590200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5467,8 +5454,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10870560" y="3198960"/>
-          <a:ext cx="4229280" cy="2590560"/>
+          <a:off x="10871280" y="3198960"/>
+          <a:ext cx="4228920" cy="2590200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5490,9 +5477,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4734000</xdr:colOff>
+      <xdr:colOff>4733640</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>2876400</xdr:rowOff>
+      <xdr:rowOff>2876040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5505,8 +5492,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10870560" y="6985800"/>
-          <a:ext cx="4734000" cy="2876400"/>
+          <a:off x="10871280" y="6985800"/>
+          <a:ext cx="4733640" cy="2876040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5528,9 +5515,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5495760</xdr:colOff>
+      <xdr:colOff>5495400</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>3008160</xdr:rowOff>
+      <xdr:rowOff>3007800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5543,8 +5530,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10870560" y="12856320"/>
-          <a:ext cx="5495760" cy="3008160"/>
+          <a:off x="10871280" y="12856320"/>
+          <a:ext cx="5495400" cy="3007800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5566,9 +5553,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5268600</xdr:colOff>
+      <xdr:colOff>5268240</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>1728720</xdr:rowOff>
+      <xdr:rowOff>1728360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5581,8 +5568,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10870560" y="17430840"/>
-          <a:ext cx="5268600" cy="1728720"/>
+          <a:off x="10871280" y="17430840"/>
+          <a:ext cx="5268240" cy="1728360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5604,9 +5591,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4819680</xdr:colOff>
+      <xdr:colOff>4819320</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>8001720</xdr:rowOff>
+      <xdr:rowOff>8001360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5619,8 +5606,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10870560" y="19750320"/>
-          <a:ext cx="4819680" cy="8001720"/>
+          <a:off x="10871280" y="19750320"/>
+          <a:ext cx="4819320" cy="8001360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5642,9 +5629,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3019320</xdr:colOff>
+      <xdr:colOff>3018960</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>1504800</xdr:rowOff>
+      <xdr:rowOff>1504440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5657,8 +5644,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10870560" y="28241640"/>
-          <a:ext cx="3019320" cy="1504800"/>
+          <a:off x="10871280" y="28241640"/>
+          <a:ext cx="3018960" cy="1504440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5680,9 +5667,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5286600</xdr:colOff>
+      <xdr:colOff>5286240</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>2562120</xdr:rowOff>
+      <xdr:rowOff>2561760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5695,8 +5682,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10870560" y="30823560"/>
-          <a:ext cx="5286600" cy="2562120"/>
+          <a:off x="10871280" y="30823560"/>
+          <a:ext cx="5286240" cy="2561760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6492,459 +6479,459 @@
   <dimension ref="A1:A133"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="87.18"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="4" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="67.7"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="87.18"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="67.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="131.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="1" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="1" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="57.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="205.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="1" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="1" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="1" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="253.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="1" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="1" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="1" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="1" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="398" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="1" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="254.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="1" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="1" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="226.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="1" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="72.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="124.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="1" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="1" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="1" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="1" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="1" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="1" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="1" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="79.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="5" t="s">
+      <c r="A94" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="358.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="1" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="1" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="1" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="1" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="110.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="1" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="1" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="1" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="359.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="1" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="1" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="4" t="s">
+      <c r="A120" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="1" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="4" t="s">
+      <c r="A123" s="1" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="1" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="1" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="1" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="1" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="1" t="s">
         <v>213</v>
       </c>
     </row>
@@ -6968,384 +6955,384 @@
   <dimension ref="A1:A132"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="80.92"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="4" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="88.11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="80.92"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="88.11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="110.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="62.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="247.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="1" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="1" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="384.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="1" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="1" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="166.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="1" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="1" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="1" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="1" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="1" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="1" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="1" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="1" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="1" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="1" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="1" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="1" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="1" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="1" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="1" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="1" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="190.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="1" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="195.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="1" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="271.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="1" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="1" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="1" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="1" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="1" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="1" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="108.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="1" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="1" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="1" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="1" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="1" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="1" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="195.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="1" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="1" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="1" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="216.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="1" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="1" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="226.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="1" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="1" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="171.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="1" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="1" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="206.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="1" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="1" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="1" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="186.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="1" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="1" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="246.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="1" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="1" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="245" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="1" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="1" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="1" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="1" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="4" t="s">
+      <c r="A120" s="1" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="262.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="4" t="s">
+      <c r="A123" s="1" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="1" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="1" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="313.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="5" t="s">
+      <c r="A127" s="3" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="245" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="1" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="1" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="1" t="s">
         <v>288</v>
       </c>
     </row>
@@ -7369,449 +7356,449 @@
   <dimension ref="A1:A118"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="102.96"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="4" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="73.04"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="102.96"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="73.04"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6"/>
+      <c r="A7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6"/>
+      <c r="A12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="4" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
+      <c r="A18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
+      <c r="A21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
+      <c r="A22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="190.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="4" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="4" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6"/>
+      <c r="A26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6"/>
+      <c r="A27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="4" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="4" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="4" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6"/>
+      <c r="A31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="4" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="4" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6"/>
+      <c r="A34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="271.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="4" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="4" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6"/>
+      <c r="A37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6"/>
+      <c r="A38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="292.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="4" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6"/>
+      <c r="A40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6"/>
+      <c r="A41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="273.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="4" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="4" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6"/>
+      <c r="A45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="309.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="4" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6"/>
+      <c r="A47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6"/>
+      <c r="A48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6"/>
+      <c r="A49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="139.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="4" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="4" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="4" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="4" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="4" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="4" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="4" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="4" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6"/>
+      <c r="A58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6"/>
+      <c r="A59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="4" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="4" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6"/>
+      <c r="A62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6"/>
+      <c r="A63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="4" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="4" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6"/>
+      <c r="A66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="93.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="4" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="4" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6"/>
+      <c r="A69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="4" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6"/>
+      <c r="A71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6"/>
+      <c r="A72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="100.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="4" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="4" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="370.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="1" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="1" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="1" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="1" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="152.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="1" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="1" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="1" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="257.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="1" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="1" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="1" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="1" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="101.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="1" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="1" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="89.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="1" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="1" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="98.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="1" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="1" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="1" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="1" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="1" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="303.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="1" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="1" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="110.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="1" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="1" t="s">
         <v>353</v>
       </c>
     </row>
@@ -7835,659 +7822,659 @@
   <dimension ref="A1:A185"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="83.24"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="4" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="112.23"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="83.24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="112.24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="189.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="118.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="1" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="1" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="207.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="1" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="1" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="1" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="189.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="1" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="1" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="1" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="1" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="1" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="1" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="171.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="1" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="1" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="1" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="1" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="1" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="1" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="1" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="1" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="1" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="191.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="1" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="1" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="1" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="1" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="1" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="227.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="1" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="1" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="1" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="1" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="228.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="1" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="293.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="1" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="1" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="263.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="1" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="1" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="1" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="1" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="1" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="1" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="1" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="1" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="1" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="1" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="1" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="1" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="1" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="1" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="1" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="1" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="1" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="1" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="1" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="1" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="1" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="1" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="1" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="1" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="1" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="1" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="1" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="1" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="1" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="1" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="1" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="1" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="118.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="1" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="1" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="1" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="222.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="1" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="1" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="1" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="1" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="1" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="1" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="1" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="1" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="1" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="1" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="213.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="1" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="1" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="1" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="1" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="1" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="4" t="s">
+      <c r="A120" s="1" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="1" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="1" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="1" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="1" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="4" t="s">
+      <c r="A127" s="1" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="186.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="1" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="1" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="1" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="146.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="1" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="231.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="1" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="1" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="1" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="258.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="1" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="4" t="s">
+      <c r="A143" s="1" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="4" t="s">
+      <c r="A144" s="1" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="4" t="s">
+      <c r="A147" s="1" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="4" t="s">
+      <c r="A148" s="1" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="1" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="4" t="s">
+      <c r="A150" s="1" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="257.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="4" t="s">
+      <c r="A153" s="1" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="4" t="s">
+      <c r="A154" s="1" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="4" t="s">
+      <c r="A155" s="1" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="4" t="s">
+      <c r="A156" s="1" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="1" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="4" t="s">
+      <c r="A158" s="1" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="300.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="4" t="s">
+      <c r="A160" s="1" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="4" t="s">
+      <c r="A161" s="1" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="4" t="s">
+      <c r="A162" s="1" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="4" t="s">
+      <c r="A166" s="1" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="4" t="s">
+      <c r="A167" s="1" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="4" t="s">
+      <c r="A168" s="1" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="4" t="s">
+      <c r="A169" s="1" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="4" t="s">
+      <c r="A170" s="1" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="100.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="4" t="s">
+      <c r="A173" s="1" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="4" t="s">
+      <c r="A174" s="1" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="4" t="s">
+      <c r="A175" s="1" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="69.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="4" t="s">
+      <c r="A177" s="1" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="95.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="4" t="s">
+      <c r="A180" s="1" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="4" t="s">
+      <c r="A181" s="1" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="4" t="s">
+      <c r="A182" s="1" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="4" t="s">
+      <c r="A183" s="1" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="4" t="s">
+      <c r="A184" s="1" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="4" t="s">
+      <c r="A185" s="1" t="s">
         <v>482</v>
       </c>
     </row>
@@ -8511,274 +8498,274 @@
   <dimension ref="A1:A69"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="73.51"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="4" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="83.24"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="4" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="73.51"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="83.24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="210.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="221.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="1" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="1" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="1" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="257.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="1" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="1" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="1" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="1" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="1" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="1" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="1" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="1" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="1" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="1" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="1" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="1" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="245" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="1" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="1" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="1" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="1" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="1" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="1" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="1" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="1" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="1" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="144.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="1" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="643" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="1" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="139.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="1" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="1" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="1" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="1" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="3" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="213.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="1" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="1" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="1" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="1" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="1" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="1" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="1" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="1" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="1" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="1" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="1" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="1" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="1" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="1" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="1" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="1" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="1" t="s">
         <v>534</v>
       </c>
     </row>
